--- a/server/apps/cmdb/support-files/model_config.xlsx
+++ b/server/apps/cmdb/support-files/model_config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="16760" tabRatio="896" firstSheet="42" activeTab="55"/>
+    <workbookView windowHeight="15820" tabRatio="896" firstSheet="43" activeTab="54"/>
   </bookViews>
   <sheets>
     <sheet name="classifications" sheetId="1" r:id="rId1"/>
@@ -205,7 +205,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12959" uniqueCount="1162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12965" uniqueCount="1166">
   <si>
     <t>模型分类ID</t>
   </si>
@@ -2230,6 +2230,20 @@
   </si>
   <si>
     <t>内网MAC地址</t>
+  </si>
+  <si>
+    <t>proc</t>
+  </si>
+  <si>
+    <t>进程</t>
+  </si>
+  <si>
+    <t>[
+{"column_id":"name","column_name":"name","column_type":"str","order":2},{"column_id":"arg","column_name":"参数","column_type":"str","order":3},{"column_id":"exe","column_name":"执行目录","column_type":"str","order":5},{"column_id":"cwd","column_name":"工作目录","column_type":"str","order":6},{"column_id":"ports","column_name":"监听端口","column_type":"str","order":4}
+]</t>
+  </si>
+  <si>
+    <t>排除系统进程</t>
   </si>
   <si>
     <t>1:1</t>
@@ -4387,7 +4401,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4412,6 +4426,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4637,7 +4654,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="中色系标题行镶边行表格样式_6e22f3" count="7" xr9:uid="{7A0FDE4A-E4C5-1C52-6C17-B2698BCD8E05}">
+    <tableStyle name="中色系标题行镶边行表格样式_6e22f3" count="7" xr9:uid="{6EF846AE-5155-A94B-DA91-BA694C07A97C}">
       <tableStyleElement type="wholeTable" dxfId="7"/>
       <tableStyleElement type="headerRow" dxfId="6"/>
       <tableStyleElement type="totalRow" dxfId="5"/>
@@ -4950,186 +4967,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16" t="s">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="19" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="19" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="19" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="19" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="19" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="19" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="19" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="19" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="19" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="19" t="s">
         <v>45</v>
       </c>
     </row>
@@ -5668,7 +5685,7 @@
         <v>215</v>
       </c>
       <c r="C4" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="D4" t="s">
         <v>397</v>
@@ -7280,7 +7297,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="B3" t="s">
         <v>213</v>
@@ -7870,10 +7887,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>343</v>
@@ -7900,10 +7917,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>343</v>
@@ -7930,10 +7947,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>343</v>
@@ -7960,10 +7977,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>343</v>
@@ -7990,10 +8007,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>343</v>
@@ -8527,10 +8544,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>343</v>
@@ -9186,7 +9203,7 @@
         <v>576</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -9213,10 +9230,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -9273,10 +9290,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -9306,7 +9323,7 @@
         <v>547</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>303</v>
@@ -9336,7 +9353,7 @@
         <v>549</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>303</v>
@@ -9366,7 +9383,7 @@
         <v>345</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>303</v>
@@ -9423,10 +9440,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>303</v>
@@ -9453,10 +9470,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>303</v>
@@ -9483,10 +9500,10 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>303</v>
@@ -9513,10 +9530,10 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>303</v>
@@ -9543,10 +9560,10 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>303</v>
@@ -10079,10 +10096,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -10109,10 +10126,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -10232,7 +10249,7 @@
         <v>576</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -10289,7 +10306,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>551</v>
@@ -10319,10 +10336,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>303</v>
@@ -10352,7 +10369,7 @@
         <v>549</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>303</v>
@@ -10382,7 +10399,7 @@
         <v>315</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>303</v>
@@ -10412,7 +10429,7 @@
         <v>529</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>303</v>
@@ -10439,10 +10456,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>303</v>
@@ -10469,10 +10486,10 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>303</v>
@@ -10499,10 +10516,10 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>303</v>
@@ -10529,10 +10546,10 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>303</v>
@@ -10559,10 +10576,10 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>303</v>
@@ -11065,10 +11082,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>303</v>
@@ -11095,10 +11112,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -11245,10 +11262,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -11278,7 +11295,7 @@
         <v>547</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -11305,10 +11322,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>303</v>
@@ -11398,7 +11415,7 @@
         <v>315</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>303</v>
@@ -11428,7 +11445,7 @@
         <v>529</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>303</v>
@@ -11455,10 +11472,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>303</v>
@@ -12239,10 +12256,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>303</v>
@@ -12269,10 +12286,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -12389,10 +12406,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -12419,10 +12436,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -12449,10 +12466,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -12479,10 +12496,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>303</v>
@@ -12509,10 +12526,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>303</v>
@@ -12539,10 +12556,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>303</v>
@@ -12569,10 +12586,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>303</v>
@@ -12599,10 +12616,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>303</v>
@@ -13105,10 +13122,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>303</v>
@@ -13195,10 +13212,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -13225,10 +13242,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -13255,10 +13272,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -13285,10 +13302,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -13318,7 +13335,7 @@
         <v>582</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -13762,10 +13779,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>303</v>
@@ -13852,10 +13869,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -13882,10 +13899,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -13912,10 +13929,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -13945,7 +13962,7 @@
         <v>582</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -14390,10 +14407,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>303</v>
@@ -14420,10 +14437,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -14450,10 +14467,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -14540,7 +14557,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>588</v>
@@ -14570,7 +14587,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>589</v>
@@ -14663,7 +14680,7 @@
         <v>369</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>303</v>
@@ -14720,10 +14737,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>303</v>
@@ -15228,10 +15245,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>303</v>
@@ -15351,7 +15368,7 @@
         <v>369</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -15381,7 +15398,7 @@
         <v>526</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -15408,10 +15425,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -15438,10 +15455,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -16395,10 +16412,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>303</v>
@@ -16515,10 +16532,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -16575,10 +16592,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>343</v>
@@ -16605,10 +16622,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>343</v>
@@ -17066,10 +17083,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>303</v>
@@ -17814,7 +17831,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -20810,7 +20827,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -21177,7 +21194,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -23544,10 +23561,10 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="B3" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="C3" t="s">
         <v>425</v>
@@ -24405,10 +24422,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>303</v>
@@ -24865,7 +24882,7 @@
         <v>547</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -24920,10 +24937,10 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -24952,7 +24969,7 @@
         <v>510</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>303</v>
@@ -24978,10 +24995,10 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>303</v>
@@ -25007,10 +25024,10 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>303</v>
@@ -25036,10 +25053,10 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>303</v>
@@ -25065,10 +25082,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>303</v>
@@ -25406,10 +25423,10 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -25435,10 +25452,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -25464,10 +25481,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -25522,10 +25539,10 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -25924,7 +25941,7 @@
         <v>547</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -25950,10 +25967,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -25979,10 +25996,10 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -26008,10 +26025,10 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -26438,10 +26455,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -26837,10 +26854,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -26869,7 +26886,7 @@
         <v>419</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -26895,10 +26912,10 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -26924,10 +26941,10 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -26953,10 +26970,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -27352,7 +27369,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>285</v>
@@ -27413,7 +27430,7 @@
         <v>345</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -27439,10 +27456,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -27780,10 +27797,10 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -28150,10 +28167,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -28182,7 +28199,7 @@
         <v>576</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -28211,7 +28228,7 @@
         <v>547</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -28266,10 +28283,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -28295,10 +28312,10 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -28636,10 +28653,10 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -28665,10 +28682,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -28694,10 +28711,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -28781,10 +28798,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -28813,7 +28830,7 @@
         <v>510</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -28839,10 +28856,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>303</v>
@@ -33302,7 +33319,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>402</v>
@@ -33688,7 +33705,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>477</v>
@@ -33746,7 +33763,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>591</v>
@@ -34117,7 +34134,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>477</v>
@@ -34175,7 +34192,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>591</v>
@@ -34207,7 +34224,7 @@
         <v>524</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -34294,7 +34311,7 @@
         <v>518</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -34320,10 +34337,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>303</v>
@@ -34662,7 +34679,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>506</v>
@@ -34723,7 +34740,7 @@
         <v>518</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -34749,10 +34766,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -35180,7 +35197,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>506</v>
@@ -35212,7 +35229,7 @@
         <v>518</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -35238,10 +35255,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -35267,10 +35284,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -35296,10 +35313,10 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -37084,7 +37101,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>402</v>
@@ -37470,10 +37487,10 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -37528,10 +37545,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -37560,7 +37577,7 @@
         <v>549</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -37589,7 +37606,7 @@
         <v>566</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>343</v>
@@ -37615,10 +37632,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>343</v>
@@ -37676,7 +37693,7 @@
         <v>529</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>343</v>
@@ -38014,10 +38031,10 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -38043,7 +38060,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>499</v>
@@ -38101,10 +38118,10 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>343</v>
@@ -38133,7 +38150,7 @@
         <v>566</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>343</v>
@@ -38159,10 +38176,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>343</v>
@@ -38220,7 +38237,7 @@
         <v>529</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>343</v>
@@ -38561,7 +38578,7 @@
         <v>475</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>343</v>
@@ -38590,7 +38607,7 @@
         <v>529</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>343</v>
@@ -38645,7 +38662,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>474</v>
@@ -38960,7 +38977,7 @@
         <v>566</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>343</v>
@@ -43232,7 +43249,7 @@
       <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="10"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="2" ht="17.65" customHeight="1" spans="1:5">
       <c r="A2" s="2" t="s">
@@ -43247,7 +43264,7 @@
       <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="11"/>
+      <c r="E2" s="12"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
@@ -43337,7 +43354,7 @@
       <c r="D8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="11"/>
+      <c r="E8" s="12"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
@@ -43367,7 +43384,7 @@
       <c r="D10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="11"/>
+      <c r="E10" s="12"/>
     </row>
     <row r="11" ht="17.65" customHeight="1" spans="1:5">
       <c r="A11" s="4" t="s">
@@ -43376,7 +43393,7 @@
       <c r="B11" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="12" t="s">
         <v>80</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -43391,7 +43408,7 @@
       <c r="B12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="12" t="s">
         <v>71</v>
       </c>
       <c r="D12" s="4" t="s">
@@ -43406,7 +43423,7 @@
       <c r="B13" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="12" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -43421,7 +43438,7 @@
       <c r="B14" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>86</v>
       </c>
       <c r="D14" s="4" t="s">
@@ -43436,7 +43453,7 @@
       <c r="B15" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="12" t="s">
         <v>89</v>
       </c>
       <c r="D15" s="4" t="s">
@@ -43451,7 +43468,7 @@
       <c r="B16" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="12" t="s">
         <v>92</v>
       </c>
       <c r="D16" s="4" t="s">
@@ -43466,7 +43483,7 @@
       <c r="B17" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="12" t="s">
         <v>95</v>
       </c>
       <c r="D17" s="4" t="s">
@@ -43641,7 +43658,7 @@
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="13" t="s">
         <v>131</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -43655,7 +43672,7 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="13" t="s">
         <v>134</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -43667,7 +43684,7 @@
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="13" t="s">
         <v>136</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -43679,7 +43696,7 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="13" t="s">
         <v>138</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -43703,7 +43720,7 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="13" t="s">
         <v>142</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -43727,7 +43744,7 @@
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="13" t="s">
+      <c r="A37" s="14" t="s">
         <v>146</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -43739,7 +43756,7 @@
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="13" t="s">
         <v>148</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -43751,7 +43768,7 @@
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="13" t="s">
         <v>150</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -43763,7 +43780,7 @@
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="13" t="s">
         <v>152</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -43775,7 +43792,7 @@
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="13" t="s">
         <v>154</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -43787,7 +43804,7 @@
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="13" t="s">
         <v>156</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -43799,7 +43816,7 @@
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="13" t="s">
         <v>158</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -43811,7 +43828,7 @@
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="12" t="s">
+      <c r="A44" s="13" t="s">
         <v>160</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -43823,7 +43840,7 @@
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="14" t="s">
+      <c r="A45" s="15" t="s">
         <v>162</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -43835,7 +43852,7 @@
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="13" t="s">
         <v>164</v>
       </c>
       <c r="B46" s="4" t="s">
@@ -43847,7 +43864,7 @@
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="13" t="s">
         <v>166</v>
       </c>
       <c r="B47" s="4" t="s">
@@ -43859,7 +43876,7 @@
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="13" t="s">
         <v>168</v>
       </c>
       <c r="B48" s="4" t="s">
@@ -43871,7 +43888,7 @@
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="12" t="s">
+      <c r="A49" s="13" t="s">
         <v>170</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -43883,7 +43900,7 @@
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="13" t="s">
         <v>172</v>
       </c>
       <c r="B50" s="4" t="s">
@@ -43895,7 +43912,7 @@
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="14" t="s">
+      <c r="A51" s="15" t="s">
         <v>174</v>
       </c>
       <c r="B51" s="4" t="s">
@@ -43907,7 +43924,7 @@
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="13" t="s">
+      <c r="A52" s="14" t="s">
         <v>176</v>
       </c>
       <c r="B52" s="4" t="s">
@@ -44493,7 +44510,7 @@
       <c r="D100" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E100" s="15"/>
+      <c r="E100" s="16"/>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="4" t="s">
@@ -44506,7 +44523,7 @@
       <c r="D101" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E101" s="15"/>
+      <c r="E101" s="16"/>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="4" t="s">
@@ -44519,7 +44536,7 @@
       <c r="D102" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E102" s="15"/>
+      <c r="E102" s="16"/>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="4" t="s">
@@ -44532,8 +44549,8 @@
       <c r="D103" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E103" s="15"/>
-      <c r="F103" s="15"/>
+      <c r="E103" s="16"/>
+      <c r="F103" s="16"/>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="4" t="s">
@@ -44546,8 +44563,8 @@
       <c r="D104" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E104" s="15"/>
-      <c r="F104" s="15"/>
+      <c r="E104" s="16"/>
+      <c r="F104" s="16"/>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="4" t="s">
@@ -44560,8 +44577,8 @@
       <c r="D105" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E105" s="15"/>
-      <c r="F105" s="15"/>
+      <c r="E105" s="16"/>
+      <c r="F105" s="16"/>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="4" t="s">
@@ -44574,8 +44591,8 @@
       <c r="D106" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E106" s="15"/>
-      <c r="F106" s="15"/>
+      <c r="E106" s="16"/>
+      <c r="F106" s="16"/>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="4" t="s">
@@ -44588,8 +44605,8 @@
       <c r="D107" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E107" s="15"/>
-      <c r="F107" s="15"/>
+      <c r="E107" s="16"/>
+      <c r="F107" s="16"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="4" t="s">
@@ -44602,8 +44619,8 @@
       <c r="D108" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E108" s="15"/>
-      <c r="F108" s="15"/>
+      <c r="E108" s="16"/>
+      <c r="F108" s="16"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="4" t="s">
@@ -44616,8 +44633,8 @@
       <c r="D109" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E109" s="15"/>
-      <c r="F109" s="15"/>
+      <c r="E109" s="16"/>
+      <c r="F109" s="16"/>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="4" t="s">
@@ -44630,8 +44647,8 @@
       <c r="D110" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E110" s="15"/>
-      <c r="F110" s="15"/>
+      <c r="E110" s="16"/>
+      <c r="F110" s="16"/>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="4" t="s">
@@ -45440,7 +45457,7 @@
       <c r="A23" t="s">
         <v>492</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="10" t="s">
         <v>493</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -59995,7 +60012,7 @@
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultColWidth="9.25" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="23.25" style="1" customWidth="1"/>
@@ -60583,18 +60600,21 @@
         <v>306</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>323</v>
+    <row r="21" ht="118" spans="1:9">
+      <c r="A21" t="s">
+        <v>675</v>
+      </c>
+      <c r="B21" t="s">
+        <v>676</v>
+      </c>
+      <c r="C21" t="s">
+        <v>386</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>677</v>
       </c>
       <c r="E21" t="s">
-        <v>322</v>
+        <v>440</v>
       </c>
       <c r="F21" s="2" t="b">
         <v>0</v>
@@ -60606,15 +60626,15 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>306</v>
+        <v>678</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
-        <v>411</v>
+        <v>335</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>323</v>
@@ -60637,16 +60657,16 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="2" t="s">
-        <v>374</v>
+        <v>411</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>375</v>
+        <v>412</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>377</v>
+        <v>323</v>
+      </c>
+      <c r="E23" t="s">
+        <v>322</v>
       </c>
       <c r="F23" s="2" t="b">
         <v>0</v>
@@ -60663,16 +60683,13 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="D24" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>377</v>
@@ -60692,16 +60709,16 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>303</v>
+        <v>380</v>
       </c>
       <c r="D25" t="s">
-        <v>304</v>
+        <v>381</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>377</v>
@@ -60720,13 +60737,33 @@
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
+      <c r="A26" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D26" t="s">
+        <v>304</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="2"/>
@@ -60754,6 +60791,15 @@
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -61229,7 +61275,7 @@
         <v>464</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
   </sheetData>
@@ -61314,7 +61360,7 @@
         <v>301</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>303</v>
@@ -61367,10 +61413,10 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>303</v>
@@ -61399,7 +61445,7 @@
         <v>350</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -61428,7 +61474,7 @@
         <v>335</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>323</v>
@@ -61451,10 +61497,10 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>323</v>
@@ -61477,10 +61523,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>323</v>
@@ -61503,10 +61549,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>323</v>
@@ -61529,10 +61575,10 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -61567,7 +61613,7 @@
         <v>331</v>
       </c>
       <c r="D12" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>305</v>
@@ -61800,7 +61846,7 @@
         <v>301</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>303</v>
@@ -61853,10 +61899,10 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>303</v>
@@ -61963,16 +62009,16 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>331</v>
       </c>
       <c r="D9" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>305</v>
@@ -62321,7 +62367,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -62378,10 +62424,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -62408,10 +62454,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -62438,10 +62484,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -62468,10 +62514,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -62498,10 +62544,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -62528,10 +62574,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -62558,10 +62604,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -62588,10 +62634,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>303</v>
@@ -62618,10 +62664,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>303</v>
@@ -62648,10 +62694,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>303</v>
@@ -62678,10 +62724,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>303</v>
@@ -62708,10 +62754,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>303</v>
@@ -63627,7 +63673,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -63684,10 +63730,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -63714,10 +63760,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -63744,10 +63790,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -63774,10 +63820,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -63804,10 +63850,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -63834,10 +63880,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -64318,7 +64364,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -64375,10 +64421,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -64405,10 +64451,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -64435,10 +64481,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -64465,10 +64511,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -64495,10 +64541,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -64525,10 +64571,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -65009,7 +65055,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -65066,10 +65112,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -65096,10 +65142,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -65126,10 +65172,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -65156,10 +65202,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -65640,7 +65686,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -65697,10 +65743,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -65727,10 +65773,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -65757,10 +65803,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -65787,10 +65833,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -65817,10 +65863,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -65847,10 +65893,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -65877,10 +65923,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -65907,10 +65953,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>303</v>
@@ -66391,7 +66437,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -66448,10 +66494,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -66478,10 +66524,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -66508,10 +66554,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -66538,10 +66584,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -66568,7 +66614,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>407</v>
@@ -66598,10 +66644,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -66628,10 +66674,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -66658,10 +66704,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>303</v>
@@ -66688,10 +66734,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>303</v>
@@ -67172,7 +67218,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -67229,10 +67275,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -67259,10 +67305,10 @@
     </row>
     <row r="9" ht="17.65" customHeight="1" spans="1:10">
       <c r="A9" s="5" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -67289,10 +67335,10 @@
     </row>
     <row r="10" ht="17.65" customHeight="1" spans="1:10">
       <c r="A10" s="5" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -67319,10 +67365,10 @@
     </row>
     <row r="11" ht="17.65" customHeight="1" spans="1:10">
       <c r="A11" s="5" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -67349,10 +67395,10 @@
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:10">
       <c r="A12" s="5" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -67833,7 +67879,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -67890,10 +67936,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -67920,10 +67966,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -67950,10 +67996,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -67980,10 +68026,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -68010,10 +68056,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -68040,10 +68086,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -68070,10 +68116,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -68100,10 +68146,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>303</v>
@@ -68584,7 +68630,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -68641,10 +68687,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -68671,10 +68717,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -68701,10 +68747,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -68731,10 +68777,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -68761,10 +68807,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -68791,10 +68837,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -68821,10 +68867,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -68851,10 +68897,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>303</v>
@@ -68881,10 +68927,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>303</v>
@@ -68911,10 +68957,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>303</v>
@@ -68941,10 +68987,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>303</v>
@@ -68971,10 +69017,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>303</v>
@@ -69001,10 +69047,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>303</v>
@@ -69485,7 +69531,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -69542,10 +69588,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -69572,10 +69618,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -69602,10 +69648,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -69632,10 +69678,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -69662,10 +69708,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -69692,10 +69738,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -69722,10 +69768,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -69752,10 +69798,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>303</v>
@@ -69782,10 +69828,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>303</v>
@@ -69812,10 +69858,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>303</v>
@@ -69842,10 +69888,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>303</v>
@@ -69872,10 +69918,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>303</v>
@@ -69902,10 +69948,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>303</v>
@@ -70386,7 +70432,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -70443,10 +70489,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -70473,10 +70519,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -70503,10 +70549,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -70533,10 +70579,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -70563,10 +70609,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -70593,10 +70639,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -70623,10 +70669,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -70653,10 +70699,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>303</v>
@@ -71259,7 +71305,7 @@
       <c r="C10" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="10" t="s">
         <v>387</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -71532,7 +71578,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -71589,10 +71635,10 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -71619,10 +71665,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -71649,10 +71695,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -71679,10 +71725,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -71709,10 +71755,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -71739,10 +71785,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -72223,7 +72269,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -72280,10 +72326,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -72310,10 +72356,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -72340,10 +72386,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -72370,10 +72416,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -72400,10 +72446,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -72430,10 +72476,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -72460,10 +72506,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -72944,7 +72990,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -73001,10 +73047,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -73031,7 +73077,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>402</v>
@@ -73061,10 +73107,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -73091,10 +73137,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -73121,10 +73167,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -73151,10 +73197,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -73635,7 +73681,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -73692,10 +73738,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -73752,10 +73798,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -73782,10 +73828,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -73812,10 +73858,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -73842,10 +73888,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -74326,7 +74372,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -74383,10 +74429,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -74413,10 +74459,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -74443,10 +74489,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -74473,10 +74519,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -74503,10 +74549,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -74533,10 +74579,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -74563,10 +74609,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -74593,10 +74639,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>303</v>
@@ -74623,10 +74669,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>303</v>
@@ -74653,10 +74699,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>303</v>
@@ -75137,7 +75183,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -75194,10 +75240,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -75224,10 +75270,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -75254,10 +75300,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -75284,10 +75330,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -75314,10 +75360,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -75344,10 +75390,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -75828,7 +75874,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -75888,7 +75934,7 @@
         <v>421</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -75915,10 +75961,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -75945,10 +75991,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -75975,10 +76021,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -76005,10 +76051,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -76035,10 +76081,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -76065,10 +76111,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -76095,10 +76141,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>303</v>
@@ -76125,10 +76171,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>303</v>
@@ -76155,10 +76201,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>303</v>
@@ -76639,7 +76685,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -76696,10 +76742,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -76726,10 +76772,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -76756,10 +76802,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -76786,10 +76832,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -76816,10 +76862,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -76846,10 +76892,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -76876,10 +76922,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -76906,10 +76952,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>303</v>
@@ -76936,10 +76982,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>303</v>
@@ -76966,10 +77012,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>303</v>
@@ -76996,10 +77042,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>303</v>
@@ -77026,10 +77072,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>303</v>
@@ -77056,10 +77102,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>303</v>
@@ -77540,7 +77586,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -77597,10 +77643,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -77627,10 +77673,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -77657,10 +77703,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -77687,10 +77733,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -77717,10 +77763,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -77747,10 +77793,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -77777,10 +77823,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -77807,10 +77853,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>303</v>
@@ -77837,10 +77883,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>303</v>
@@ -77867,10 +77913,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>303</v>
@@ -78351,7 +78397,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -78408,10 +78454,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -78438,10 +78484,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -78468,10 +78514,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -78498,10 +78544,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -78528,10 +78574,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -78558,10 +78604,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -78588,10 +78634,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -78618,10 +78664,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>303</v>
@@ -78648,10 +78694,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>303</v>
@@ -78678,10 +78724,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>303</v>
@@ -78708,10 +78754,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>303</v>
@@ -79439,7 +79485,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -79496,10 +79542,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -79526,10 +79572,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -79556,10 +79602,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -79586,10 +79632,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -79616,10 +79662,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -79646,10 +79692,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -80130,7 +80176,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -80187,10 +80233,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -80217,10 +80263,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -80247,10 +80293,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -80307,10 +80353,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -80337,10 +80383,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>303</v>
@@ -80367,10 +80413,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>303</v>
@@ -80397,10 +80443,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>303</v>
@@ -80427,10 +80473,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>303</v>
@@ -80911,7 +80957,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -80968,10 +81014,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -80998,10 +81044,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -81028,10 +81074,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -81058,10 +81104,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -81481,10 +81527,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>303</v>
@@ -81938,16 +81984,16 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>303</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>322</v>
@@ -82420,10 +82466,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>343</v>
@@ -82450,16 +82496,16 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>331</v>
       </c>
       <c r="D6" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>305</v>
@@ -82480,16 +82526,16 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>331</v>
       </c>
       <c r="D7" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>305</v>
@@ -83262,10 +83308,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>303</v>
@@ -83325,7 +83371,7 @@
         <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -83352,10 +83398,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>303</v>
@@ -83382,10 +83428,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>
@@ -83412,10 +83458,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>303</v>
@@ -83442,10 +83488,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -83472,10 +83518,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>303</v>
@@ -83502,10 +83548,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>303</v>
@@ -87639,10 +87685,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>303</v>
@@ -87672,7 +87718,7 @@
         <v>518</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>303</v>
@@ -88101,7 +88147,7 @@
         <v>512</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>303</v>
@@ -88158,10 +88204,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>303</v>
@@ -89291,7 +89337,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>472</v>
@@ -90164,10 +90210,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>303</v>

--- a/server/apps/cmdb/support-files/model_config.xlsx
+++ b/server/apps/cmdb/support-files/model_config.xlsx
@@ -2239,7 +2239,7 @@
   </si>
   <si>
     <t>[
-{"column_id":"name","column_name":"name","column_type":"str","order":2},{"column_id":"arg","column_name":"参数","column_type":"str","order":3},{"column_id":"exe","column_name":"执行目录","column_type":"str","order":5},{"column_id":"cwd","column_name":"工作目录","column_type":"str","order":6},{"column_id":"ports","column_name":"监听端口","column_type":"str","order":4}
+{"column_id":"pid","column_name":"PID","column_type":"number","order":2},{"column_id":"name","column_name":"name","column_type":"str","order":1},{"column_id":"arg","column_name":"参数","column_type":"str","order":3},{"column_id":"exe","column_name":"执行目录","column_type":"str","order":5},{"column_id":"cwd","column_name":"工作目录","column_type":"str","order":6},{"column_id":"ports","column_name":"监听端口","column_type":"str","order":4}
 ]</t>
   </si>
   <si>
@@ -4654,7 +4654,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="中色系标题行镶边行表格样式_6e22f3" count="7" xr9:uid="{6EF846AE-5155-A94B-DA91-BA694C07A97C}">
+    <tableStyle name="中色系标题行镶边行表格样式_6e22f3" count="7" xr9:uid="{9A5807D5-AEA3-DA3B-24A0-BB6943985E97}">
       <tableStyleElement type="wholeTable" dxfId="7"/>
       <tableStyleElement type="headerRow" dxfId="6"/>
       <tableStyleElement type="totalRow" dxfId="5"/>
@@ -60600,7 +60600,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="21" ht="118" spans="1:9">
+    <row r="21" ht="135" spans="1:9">
       <c r="A21" t="s">
         <v>675</v>
       </c>
